--- a/tests/e2e/fixtures/gridcraft/sales-sample.xlsx
+++ b/tests/e2e/fixtures/gridcraft/sales-sample.xlsx
@@ -1209,7 +1209,11 @@
   </sheetData>
   <conditionalFormatting sqref="H5:H10">
     <cfRule type="iconSet" priority="1">
-      <iconSet iconSet="3Arrows"/>
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G10">
